--- a/data/raw/data_articles/datajournal_articles git V final_4.xlsx
+++ b/data/raw/data_articles/datajournal_articles git V final_4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bliv10\Desktop\DCC github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bliv10\Desktop\Github Data Articles Blanka\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B9CF96-AEF2-4CF5-88E0-AE5C0F51BC74}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA33BAC1-D4EA-4329-A850-5DB8EBCC578D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data_sum" sheetId="4" r:id="rId1"/>
@@ -25,11 +25,14 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -128,37 +131,37 @@
     <t>Article number</t>
   </si>
   <si>
-    <t>Charite article doi</t>
-  </si>
-  <si>
     <t>N reuse</t>
   </si>
   <si>
-    <t>Applicable (1 = yes, 0 = no [no data])</t>
-  </si>
-  <si>
     <t>N citations on last checked date</t>
   </si>
   <si>
-    <t>N excluded due to foreign lang.</t>
-  </si>
-  <si>
     <t>N excluded due to limited access</t>
   </si>
   <si>
     <t>N went offline since checking</t>
   </si>
   <si>
-    <t>N excluded due to too many references from citing article to dataset article</t>
-  </si>
-  <si>
-    <t>ratio N reuse/articles checked</t>
-  </si>
-  <si>
-    <t>extrapolated number of missed indirect citations</t>
-  </si>
-  <si>
-    <t>extrapolated number of indirect citations overall</t>
+    <t>Data article DOI</t>
+  </si>
+  <si>
+    <t>Applicable</t>
+  </si>
+  <si>
+    <t>N excluded due to foreign language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N excluded due to too many references from citing article </t>
+  </si>
+  <si>
+    <t>Ratio N reuse/articles checked</t>
+  </si>
+  <si>
+    <t>Extrapolated number of missed indirect citations</t>
+  </si>
+  <si>
+    <t>Extrapolated number of indirect citations overall</t>
   </si>
 </sst>
 </file>
@@ -723,9 +726,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -763,7 +766,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -869,7 +872,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1011,7 +1014,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1020,43 +1023,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A25E17AF-E765-478D-AA2D-38199D8DBA61}">
   <dimension ref="A1:L29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.453125" customWidth="1"/>
-    <col min="2" max="2" width="28.54296875" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" customWidth="1"/>
-    <col min="6" max="6" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="9.81640625" customWidth="1"/>
-    <col min="8" max="8" width="16.54296875" customWidth="1"/>
-    <col min="9" max="9" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="14.44140625" customWidth="1"/>
+    <col min="2" max="2" width="28.5546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.77734375" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" customWidth="1"/>
+    <col min="6" max="6" width="13.5546875" customWidth="1"/>
+    <col min="7" max="7" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="16.5546875" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="39.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>29</v>
       </c>
       <c r="B1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" t="s">
         <v>31</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" t="s">
         <v>32</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="I1" t="s">
         <v>37</v>
@@ -1071,7 +1074,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1185,7 +1188,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1223,7 +1226,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1261,7 +1264,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1299,7 +1302,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1337,7 +1340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1371,7 +1374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1412,7 +1415,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1450,7 +1453,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1516,7 +1519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1550,7 +1553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1591,7 +1594,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1625,7 +1628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1659,7 +1662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1693,7 +1696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1761,7 +1764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1828,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1862,7 +1865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1937,7 +1940,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1971,7 +1974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2005,7 +2008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2039,7 +2042,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2079,12 +2082,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a0e84d40-090a-490d-8a02-2942ffba970a" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaacefca-f467-416c-abd0-2b181dff1e20">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2283,29 +2288,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a0e84d40-090a-490d-8a02-2942ffba970a" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaacefca-f467-416c-abd0-2b181dff1e20">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{647AA23E-A486-48B9-BA40-113933E28953}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29E293C4-885E-47C7-B36A-6AC1C731FF01}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C2D3F5D9-F66A-401E-BC58-4588B5177296}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2314,4 +2305,31 @@
     <ds:schemaRef ds:uri="aaacefca-f467-416c-abd0-2b181dff1e20"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29E293C4-885E-47C7-B36A-6AC1C731FF01}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aaacefca-f467-416c-abd0-2b181dff1e20"/>
+    <ds:schemaRef ds:uri="a0e84d40-090a-490d-8a02-2942ffba970a"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{647AA23E-A486-48B9-BA40-113933E28953}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>